--- a/csv_file_comparison_filled_jean.xlsx
+++ b/csv_file_comparison_filled_jean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JMende95\Downloads\csv comparison_krishna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20E1041-346D-4DA2-BE23-59FFC86DF6BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5C8699-3114-4E69-A823-648288043F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANTHEM" sheetId="1" r:id="rId1"/>
@@ -54,10 +54,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={3C256A91-8352-4F0F-A48C-A5D356831A1C}</author>
+    <author>tc={BE03D684-5D31-4429-81D3-20835E96DB5E}</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{BE03D684-5D31-4429-81D3-20835E96DB5E}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -70,33 +70,6 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={EB4844B9-8837-4208-9206-65CEEC105F34}</author>
-    <author>tc={FA6DCA48-D417-46BD-A3E9-2F7E6A678C00}</author>
-  </authors>
-  <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    /domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/anthem_uc/anthem_uc_extracted_scores.csv</t>
-      </text>
-    </comment>
-    <comment ref="C2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    https://dsa-staging.jnj.com/#collection/687fe830e4f52ab6376b2785/folder/6a2047b8d18b0be7e502470a</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={92791AC7-D733-4601-8652-1F62E0ABA181}</author>
@@ -123,7 +96,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={F922AD8C-3A96-4D6E-A41D-8AA59BF2A58B}</author>
@@ -150,7 +123,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={86C4EFC4-7FBC-490D-9D96-1E1F2455F9AC}</author>
@@ -178,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="408">
   <si>
     <t>ANTHEM-UC</t>
   </si>
@@ -1089,20 +1062,326 @@
     <t>2791 obs</t>
   </si>
   <si>
-    <t>weeks 0, 4, 8, 12, 16, 20, 24, 28, 32, 36, 40, 44, 48</t>
-  </si>
-  <si>
-    <t>xxxx</t>
-  </si>
-  <si>
-    <t>CNTO1959UCO3004_astro_inferred_visit_ard_20261026.csv</t>
+    <t>CNTO1959UCO3004_astro_wk24_ard_20261026</t>
+  </si>
+  <si>
+    <t>QUASAR [ARD]</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MES_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYO_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_PGSCORE_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_UCEIS_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_VASCULAR_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_EROSION_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_BLEEDING_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_RHI_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_NANCYHI_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_GBTOT_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_GBLO_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_GBHI_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_HSTL_AVAL</t>
+  </si>
+  <si>
+    <t>ADHIST_PARAMCD_MHL_AVAL</t>
+  </si>
+  <si>
+    <t>ADLB_PARAMCD_CRP_AVAL</t>
+  </si>
+  <si>
+    <t>ADLB_PARAMCD_CALPT_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_RECTUM_CENTRAL_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_SIGMOID_ADJUDICATOR_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_SIGMOID_CENTRAL_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_EXTENT_AVALC</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ENNRM_AVALC</t>
+  </si>
+  <si>
+    <t>ADSL_CONTINENT</t>
+  </si>
+  <si>
+    <t>ADSL_SITEID</t>
+  </si>
+  <si>
+    <t>ADSL_TRT01P</t>
+  </si>
+  <si>
+    <t>ADSL_TRT01PN</t>
+  </si>
+  <si>
+    <t>ADSL_TRT02PN</t>
+  </si>
+  <si>
+    <t>ADSL_TRT01A</t>
+  </si>
+  <si>
+    <t>ADSL_TRT01AN</t>
+  </si>
+  <si>
+    <t>ADSL_TRT02A</t>
+  </si>
+  <si>
+    <t>ADSL_TRT02AN</t>
+  </si>
+  <si>
+    <t>ADSL_ARM</t>
+  </si>
+  <si>
+    <t>ADSL_NTREATFL</t>
+  </si>
+  <si>
+    <t>ADSL_RANDFL</t>
+  </si>
+  <si>
+    <t>ADSL_FASFL</t>
+  </si>
+  <si>
+    <t>ADSL_SAFFL</t>
+  </si>
+  <si>
+    <t>ADSL_RESFL</t>
+  </si>
+  <si>
+    <t>ADSL_CSUSEFL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_COLON_DES_CENTRAL_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_COLON_TRA_ADJUDICATOR_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_COLON_ASC_CENTRAL_AVAL</t>
+  </si>
+  <si>
+    <t>ASTRO_PARAMCD_COLON_DES_ADJUDICATOR_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MES_ReaderC_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MES_ReaderL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_REM_AVALC</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_RES_AVALC</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_EHL_AVALC</t>
+  </si>
+  <si>
+    <t>ENCSCORE</t>
+  </si>
+  <si>
+    <t>ENFSCORE</t>
+  </si>
+  <si>
+    <t>ENLCSCOR</t>
+  </si>
+  <si>
+    <t>ENLSCORE</t>
+  </si>
+  <si>
+    <t>ENSCORE</t>
+  </si>
+  <si>
+    <t>SMAYO</t>
+  </si>
+  <si>
+    <t>UCEIS_UCEISSC</t>
+  </si>
+  <si>
+    <t>UCEIS_UCEIS4</t>
+  </si>
+  <si>
+    <t>HIST_CHRIINF</t>
+  </si>
+  <si>
+    <t>HIST_EOS</t>
+  </si>
+  <si>
+    <t>HIST_GBLO</t>
+  </si>
+  <si>
+    <t>HIST_NEUTEP</t>
+  </si>
+  <si>
+    <t>HIST_NEUTLP</t>
+  </si>
+  <si>
+    <t>HIST_ULCER</t>
+  </si>
+  <si>
+    <t>HIST_HEHL</t>
+  </si>
+  <si>
+    <t>HIST_HIHL</t>
+  </si>
+  <si>
+    <t>IBREM</t>
+  </si>
+  <si>
+    <t>IBREMM</t>
+  </si>
+  <si>
+    <t>BIO_CALNRM</t>
+  </si>
+  <si>
+    <t>BIO_CRPNRM</t>
+  </si>
+  <si>
+    <t>OUT_CFREMP</t>
+  </si>
+  <si>
+    <t>OUT_CREMFP</t>
+  </si>
+  <si>
+    <t>OUT_CREMLP</t>
+  </si>
+  <si>
+    <t>OUT_CREMP</t>
+  </si>
+  <si>
+    <t>OUT_CRESPAP</t>
+  </si>
+  <si>
+    <t>OUT_CRESPLP</t>
+  </si>
+  <si>
+    <t>OUT_CRESPP</t>
+  </si>
+  <si>
+    <t>OUT_ENHLP</t>
+  </si>
+  <si>
+    <t>OUT_ENNRMP</t>
+  </si>
+  <si>
+    <t>OUT_PMRESPP</t>
+  </si>
+  <si>
+    <t>OUT_SREMAP</t>
+  </si>
+  <si>
+    <t>OUT_SREMP</t>
+  </si>
+  <si>
+    <t>OUT_SRESPAP</t>
+  </si>
+  <si>
+    <t>OUT_SRESPP</t>
+  </si>
+  <si>
+    <t>TRT03P</t>
+  </si>
+  <si>
+    <t>TRT03PN</t>
+  </si>
+  <si>
+    <t>TRT03A</t>
+  </si>
+  <si>
+    <t>TRT03AN</t>
+  </si>
+  <si>
+    <t>TRT04P</t>
+  </si>
+  <si>
+    <t>TRT04PN</t>
+  </si>
+  <si>
+    <t>TRT04A</t>
+  </si>
+  <si>
+    <t>TRT04AN</t>
+  </si>
+  <si>
+    <t>TRTSEQPN</t>
+  </si>
+  <si>
+    <t>TRTSEQA</t>
+  </si>
+  <si>
+    <t>TRTSEQAN</t>
+  </si>
+  <si>
+    <t>RAND1FL</t>
+  </si>
+  <si>
+    <t>RAND2FL</t>
+  </si>
+  <si>
+    <t>FAS1FL</t>
+  </si>
+  <si>
+    <t>FAS2FL</t>
+  </si>
+  <si>
+    <t>SAF1FL</t>
+  </si>
+  <si>
+    <t>SAF2FL</t>
+  </si>
+  <si>
+    <t>TREAT1FL</t>
+  </si>
+  <si>
+    <t>TREAT2FL</t>
+  </si>
+  <si>
+    <t>NRW12FL</t>
+  </si>
+  <si>
+    <t>quasar_extracted_scores.csv</t>
+  </si>
+  <si>
+    <t>CNTO1959UCO3001_quasar_lte_wk188_ard_merged_20261020</t>
+  </si>
+  <si>
+    <t>QUASAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1133,13 +1412,26 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1162,7 +1454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1196,9 +1488,11 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1394,6 +1688,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44536644-EC22-2851-71C0-476506419CA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2076450</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51163E6A-220F-37F4-DD75-EFB4387036F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1645,6 +1993,114 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{661D260F-E687-C6EB-B06E-875D11B87412}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9839325" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2362200</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF499F4-FE1A-49AA-8374-E49C7E8B6A0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8867775" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1660,7 +2116,7 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2076450</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1709,7 +2165,7 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2076450</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1763,7 +2219,7 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2076450</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1817,7 +2273,7 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>2076450</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1826,6 +2282,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87CCE8DE-4E70-9B23-EB76-9CBE78F74CCC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2076450</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B4DE84C-EA62-7625-3484-9CDE8201BB52}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2077,6 +2587,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2076450</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2196B8FC-B8F8-6BAE-7770-5DE51407BA95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2258,6 +2822,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F94DC47-A462-F1CE-2F35-543EA5AE203D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2076450</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45D74AB-F164-EBFD-8931-C673FFA67985}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2509,6 +3127,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2076450</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6768971-B3E1-58B9-0A50-1295ACDDC8FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9525000" cy="9525000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2724,24 +3396,13 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B2" dT="2026-10-22T17:27:17.23" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{3C256A91-8352-4F0F-A48C-A5D356831A1C}">
+  <threadedComment ref="B2" dT="2026-10-22T17:27:17.23" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{BE03D684-5D31-4429-81D3-20835E96DB5E}">
     <text>/domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/astro/astro_extracted_scores.csv</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B2" dT="2026-10-22T12:51:40.61" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{EB4844B9-8837-4208-9206-65CEEC105F34}">
-    <text>/domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/anthem_uc/anthem_uc_extracted_scores.csv</text>
-  </threadedComment>
-  <threadedComment ref="C2" dT="2026-10-22T15:16:19.58" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{FA6DCA48-D417-46BD-A3E9-2F7E6A678C00}">
-    <text>https://dsa-staging.jnj.com/#collection/687fe830e4f52ab6376b2785/folder/6a2047b8d18b0be7e502470a</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
-<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-10-22T12:51:40.61" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{92791AC7-D733-4601-8652-1F62E0ABA181}">
     <text>/domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/anthem_uc/anthem_uc_extracted_scores.csv</text>
@@ -2752,7 +3413,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-10-22T12:51:40.61" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{F922AD8C-3A96-4D6E-A41D-8AA59BF2A58B}">
     <text>/domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/anthem_uc/anthem_uc_extracted_scores.csv</text>
@@ -2763,7 +3424,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="B2" dT="2026-10-22T12:51:40.61" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{86C4EFC4-7FBC-490D-9D96-1E1F2455F9AC}">
     <text>/domino/datasets/local/cv_endoscopy/kchaita6/IBD/UlcerativeColitis/CODE/colab/uc_work/uc_trials_metafiles_labels/anthem_uc/anthem_uc_extracted_scores.csv</text>
@@ -3900,60 +4561,60 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28" style="1" customWidth="1"/>
-    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.140625" customWidth="1"/>
+    <col min="2" max="2" width="28" style="9" customWidth="1"/>
+    <col min="3" max="3" width="42.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" style="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>305</v>
+      <c r="C2" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>304</v>
+      <c r="B3" s="9">
+        <v>574</v>
+      </c>
+      <c r="C3" s="9">
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>303</v>
+      <c r="C4" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3961,844 +4622,844 @@
       <c r="A6" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>304</v>
+      <c r="C6" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>304</v>
+      <c r="C7" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>304</v>
+      <c r="C8" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>304</v>
+      <c r="C9" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>304</v>
+      <c r="C10" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>304</v>
+      <c r="C11" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>304</v>
+      <c r="C12" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>304</v>
+      <c r="C13" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>304</v>
+      <c r="C14" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>304</v>
+      <c r="C15" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>304</v>
+      <c r="C16" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>304</v>
+      <c r="C17" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>304</v>
+      <c r="C18" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>304</v>
+      <c r="C19" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>304</v>
+      <c r="C20" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>304</v>
+      <c r="C21" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>304</v>
+      <c r="C22" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>304</v>
+      <c r="C23" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>304</v>
+      <c r="C24" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>304</v>
+      <c r="C25" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>304</v>
+      <c r="C26" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>304</v>
+      <c r="C27" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>304</v>
+      <c r="C28" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>304</v>
+      <c r="C29" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>304</v>
+      <c r="C30" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>304</v>
+      <c r="C31" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>304</v>
+      <c r="C32" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>304</v>
+      <c r="C33" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>139</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>304</v>
+      <c r="C34" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>304</v>
+      <c r="C35" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>141</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>304</v>
+      <c r="C36" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>142</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>304</v>
+      <c r="C37" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>304</v>
+      <c r="C38" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>304</v>
+      <c r="C39" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>304</v>
+      <c r="C40" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>146</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>304</v>
+      <c r="C41" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>147</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>304</v>
+      <c r="C42" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>304</v>
+      <c r="C43" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>304</v>
+      <c r="C44" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>304</v>
+      <c r="C45" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>304</v>
+      <c r="C46" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>304</v>
+      <c r="C47" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>304</v>
+      <c r="C48" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>148</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>304</v>
+      <c r="C49" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>149</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>304</v>
+      <c r="C50" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>150</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>304</v>
+      <c r="C51" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>151</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C52" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>304</v>
+      <c r="C52" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C53" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>304</v>
+      <c r="C53" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>152</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>304</v>
+      <c r="C54" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>153</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>304</v>
+      <c r="C55" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>154</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C56" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>304</v>
+      <c r="C56" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>155</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>304</v>
+      <c r="C57" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>156</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>304</v>
+      <c r="C58" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>157</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C59" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D59" s="13" t="s">
-        <v>304</v>
+      <c r="C59" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>158</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>304</v>
+      <c r="C60" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>159</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>304</v>
+      <c r="C61" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C62" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>304</v>
+      <c r="C62" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>161</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C63" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>304</v>
+      <c r="C63" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>162</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D64" s="13" t="s">
-        <v>304</v>
+      <c r="C64" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>163</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="C65" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="D65" s="13" t="s">
-        <v>304</v>
+      <c r="C65" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -4807,30 +5468,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D80"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>1</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>405</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4865,44 +5526,44 @@
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>165</v>
+        <v>351</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>167</v>
+        <v>352</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>353</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>111</v>
@@ -4913,10 +5574,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>354</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>111</v>
@@ -4926,11 +5587,11 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>19</v>
+      <c r="A10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>111</v>
@@ -4940,8 +5601,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
+      <c r="A11" t="s">
+        <v>114</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>111</v>
@@ -4954,8 +5615,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
+      <c r="A12" t="s">
+        <v>34</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>111</v>
@@ -4968,8 +5629,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>24</v>
+      <c r="A13" t="s">
+        <v>115</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>111</v>
@@ -4982,8 +5643,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
+      <c r="A14" t="s">
+        <v>49</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>111</v>
@@ -4996,8 +5657,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
+      <c r="A15" t="s">
+        <v>116</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>111</v>
@@ -5010,8 +5671,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
+      <c r="A16" t="s">
+        <v>117</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>111</v>
@@ -5024,8 +5685,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>31</v>
+      <c r="A17" t="s">
+        <v>356</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>111</v>
@@ -5038,8 +5699,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>33</v>
+      <c r="A18" t="s">
+        <v>119</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>111</v>
@@ -5052,8 +5713,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>34</v>
+      <c r="A19" t="s">
+        <v>120</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>111</v>
@@ -5066,8 +5727,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>35</v>
+      <c r="A20" t="s">
+        <v>357</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>111</v>
@@ -5080,8 +5741,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
+      <c r="A21" t="s">
+        <v>121</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>111</v>
@@ -5094,8 +5755,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>38</v>
+      <c r="A22" t="s">
+        <v>358</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>111</v>
@@ -5108,8 +5769,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>39</v>
+      <c r="A23" t="s">
+        <v>359</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>111</v>
@@ -5122,8 +5783,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>40</v>
+      <c r="A24" t="s">
+        <v>360</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>111</v>
@@ -5136,8 +5797,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>41</v>
+      <c r="A25" t="s">
+        <v>125</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>111</v>
@@ -5150,8 +5811,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>42</v>
+      <c r="A26" t="s">
+        <v>361</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>111</v>
@@ -5164,8 +5825,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>43</v>
+      <c r="A27" t="s">
+        <v>124</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>111</v>
@@ -5178,8 +5839,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>44</v>
+      <c r="A28" t="s">
+        <v>123</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>111</v>
@@ -5192,8 +5853,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>45</v>
+      <c r="A29" t="s">
+        <v>362</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>111</v>
@@ -5206,8 +5867,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>46</v>
+      <c r="A30" t="s">
+        <v>363</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>111</v>
@@ -5220,8 +5881,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>47</v>
+      <c r="A31" t="s">
+        <v>122</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>111</v>
@@ -5234,8 +5895,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>49</v>
+      <c r="A32" t="s">
+        <v>364</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>111</v>
@@ -5248,8 +5909,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>50</v>
+      <c r="A33" t="s">
+        <v>365</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>111</v>
@@ -5262,8 +5923,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>51</v>
+      <c r="A34" t="s">
+        <v>366</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>111</v>
@@ -5276,8 +5937,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>52</v>
+      <c r="A35" t="s">
+        <v>78</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>111</v>
@@ -5290,8 +5951,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>53</v>
+      <c r="A36" t="s">
+        <v>79</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>111</v>
@@ -5304,8 +5965,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>54</v>
+      <c r="A37" t="s">
+        <v>80</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>111</v>
@@ -5318,8 +5979,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>55</v>
+      <c r="A38" t="s">
+        <v>81</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>111</v>
@@ -5332,8 +5993,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>56</v>
+      <c r="A39" t="s">
+        <v>82</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>111</v>
@@ -5347,7 +6008,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>367</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>111</v>
@@ -5361,7 +6022,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>368</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>111</v>
@@ -5375,7 +6036,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>111</v>
@@ -5389,7 +6050,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>111</v>
@@ -5403,7 +6064,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>111</v>
@@ -5417,7 +6078,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>370</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>111</v>
@@ -5431,7 +6092,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>65</v>
+        <v>371</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>111</v>
@@ -5445,7 +6106,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>372</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>111</v>
@@ -5459,7 +6120,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>373</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>111</v>
@@ -5473,7 +6134,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>374</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>111</v>
@@ -5487,7 +6148,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>71</v>
+        <v>375</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>111</v>
@@ -5501,7 +6162,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>376</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>111</v>
@@ -5515,7 +6176,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>377</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>111</v>
@@ -5529,7 +6190,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>378</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>111</v>
@@ -5543,7 +6204,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>111</v>
@@ -5557,7 +6218,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>380</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>111</v>
@@ -5571,7 +6232,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>111</v>
@@ -5585,7 +6246,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>111</v>
@@ -5599,7 +6260,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>383</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>111</v>
@@ -5613,7 +6274,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>111</v>
@@ -5627,7 +6288,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>111</v>
@@ -5641,7 +6302,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>111</v>
@@ -5655,7 +6316,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>111</v>
@@ -5669,7 +6330,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>111</v>
@@ -5683,7 +6344,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>111</v>
@@ -5697,7 +6358,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>111</v>
@@ -5711,7 +6372,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>111</v>
@@ -5725,7 +6386,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>111</v>
@@ -5739,7 +6400,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>111</v>
@@ -5753,7 +6414,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>111</v>
@@ -5767,7 +6428,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>111</v>
@@ -5781,7 +6442,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>111</v>
@@ -5795,7 +6456,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>111</v>
@@ -5809,7 +6470,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>111</v>
@@ -5823,7 +6484,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>111</v>
@@ -5837,7 +6498,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>385</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>111</v>
@@ -5851,7 +6512,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>386</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>111</v>
@@ -5865,7 +6526,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>111</v>
@@ -5879,7 +6540,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>104</v>
+        <v>388</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>111</v>
@@ -5893,7 +6554,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>389</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>111</v>
@@ -5907,22 +6568,259 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>390</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>391</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>392</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>107</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D80" s="5" t="s">
+      <c r="B83" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>393</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>394</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>395</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>396</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>397</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>398</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>399</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>400</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>401</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>402</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>403</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>404</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>160</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D97" s="5" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/csv_file_comparison_filled_jean.xlsx
+++ b/csv_file_comparison_filled_jean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JMende95\Downloads\csv comparison_krishna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F076E1-1161-4A32-9821-F0B9A876E1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AA2735-9C2C-424E-80EF-7000B1835869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANTHEM" sheetId="1" r:id="rId1"/>
@@ -118,8 +118,26 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={3980D9DB-09BC-4029-AE3B-CE182DCD9F7E}</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{3980D9DB-09BC-4029-AE3B-CE182DCD9F7E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://dsa-staging.jnj.com/#collection/687fe830e4f52ab6376b2785/folder/68ef30f66f2fe1bb7c4f14f1</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="576">
   <si>
     <t>ANTHEM-UC</t>
   </si>
@@ -1699,6 +1717,157 @@
   </si>
   <si>
     <t>54781532UCO2001_jak_uc_wk32_ard_slim_20261027.csv</t>
+  </si>
+  <si>
+    <t>weeks 0, 2, 4, 8, 12, 16</t>
+  </si>
+  <si>
+    <t>weeks 0, 1,  2, 3, 4, 8, 12, 16, 24, 28, 32, 36, 40, 44, 48, 52, 56, 60...
+64, 68, 72, 76, 80, 84, 88, 92, 96, 100, 104, 112, 116, 120, 124, 128, 132, 136, 140... 144, 148, 152, 156, 160, 164, 168, 172, 176, 180, 184, 188, 192, 196, 200</t>
+  </si>
+  <si>
+    <t>ADMAYO_SAS7BDAT_PARAMCD_ENLSCORL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_SAS7BDAT_PARAMCD_ENSCOREL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ABSSLE3_AVALC</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_SFSCORTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ABSSTLL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ABSSTLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ABSSTOOL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ENLSCLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_ENSCOLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYOL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYOLE_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYOLEL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYOLETF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MAYOLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MMAYOL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_MMAYOLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_NUMMAYO_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_NUMMAYOL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_NUMMMAYO_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_NUMPMAYO_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_PGSCOLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_PGSCOREL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_PMAYOL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_PMAYOLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_RBSCOREL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_RBSCORTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_PARAMCD_SFSCOREL_AVAL</t>
+  </si>
+  <si>
+    <t>ADMAYO_XPT_PARAMCD_PMAYOREM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CALLNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CALNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CALTNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CRPLNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CRPNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CRPTNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTFLNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTFNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTFTNORM_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CALPT_AVAL</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CRPL_AVAL</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CRPLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTFL_AVAL</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_LTFT_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_UCEISL_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_UCEISLTF_AVAL</t>
+  </si>
+  <si>
+    <t>ADUCEIS_PARAMCD_UCEISLE4_AVALC</t>
+  </si>
+  <si>
+    <t>ADLBEF_PARAMCD_CALPL_AVAL</t>
+  </si>
+  <si>
+    <t>CNTO1275UCO3001_unifi_wk200_ard_merged_slim_20261027</t>
   </si>
 </sst>
 </file>
@@ -1738,6 +1907,7 @@
     <font>
       <sz val="8"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1750,6 +1920,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1778,7 +1949,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1822,6 +1993,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4528,6 +4702,20 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="C2" dT="2026-10-28T02:07:45.02" personId="{8B5B4908-A960-4B6D-9057-7102DEAF3518}" id="{3980D9DB-09BC-4029-AE3B-CE182DCD9F7E}">
+    <text>https://dsa-staging.jnj.com/#collection/687fe830e4f52ab6376b2785/folder/68ef30f66f2fe1bb7c4f14f1</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>1248678909</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="96" url="https://dsa-staging.jnj.com/#collection/687fe830e4f52ab6376b2785/folder/68ef30f66f2fe1bb7c4f14f1"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D80"/>
@@ -6567,7 +6755,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="66.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.85546875" customWidth="1"/>
   </cols>
@@ -8007,7 +8195,7 @@
       <c r="C7" s="6">
         <v>434</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>479</v>
       </c>
     </row>
@@ -8663,50 +8851,55 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="67.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="11" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>418</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="6">
+        <v>961</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1"/>
+      <c r="B4" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>527</v>
+      </c>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -8715,632 +8908,1097 @@
       <c r="B5" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>87</v>
+      <c r="B6" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C6" s="7">
+        <v>961</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>87</v>
+      <c r="B7" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C7" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>87</v>
+      <c r="B8" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C8" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>421</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>87</v>
+      <c r="B9" s="6">
+        <v>5100</v>
+      </c>
+      <c r="C9" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>87</v>
+      <c r="B10" s="6">
+        <v>2243</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3504</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>422</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>87</v>
+      <c r="B11" s="6">
+        <v>2346</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5683</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>265</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>87</v>
+      <c r="B12" s="6">
+        <v>2265</v>
+      </c>
+      <c r="C12" s="7">
+        <v>3955</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>423</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>87</v>
+      <c r="B13" s="6">
+        <v>2346</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3693</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>424</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>87</v>
+      <c r="B14" s="6">
+        <v>2346</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3692</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>87</v>
+      <c r="B15" s="6">
+        <v>2265</v>
+      </c>
+      <c r="C15" s="7">
+        <v>3955</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>425</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>2346</v>
+      </c>
+      <c r="C16" s="7">
+        <v>3693</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
+        <v>2258</v>
+      </c>
+      <c r="C17" s="7">
+        <v>3916</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>426</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C18" s="7">
+        <v>4425</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>427</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="6">
+        <v>2258</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3916</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>428</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C20" s="7">
+        <v>14750</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>429</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C21" s="7">
+        <v>14750</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>430</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3692</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <v>2258</v>
+      </c>
+      <c r="C23" s="7">
+        <v>3916</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>431</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C24" s="7">
+        <v>4425</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>432</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25" s="6">
+        <v>2338</v>
+      </c>
+      <c r="C25" s="7">
+        <v>3692</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6">
+        <v>2340</v>
+      </c>
+      <c r="C26" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>434</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
+        <v>2340</v>
+      </c>
+      <c r="C27" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>435</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
+        <v>2340</v>
+      </c>
+      <c r="C28" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>436</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="6">
+        <v>4262</v>
+      </c>
+      <c r="C29" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C30" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6">
+        <v>5099</v>
+      </c>
+      <c r="C31" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>438</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C32" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
+        <v>4142</v>
+      </c>
+      <c r="C33" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>439</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>4258</v>
+      </c>
+      <c r="C34" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>440</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="6">
+        <v>4258</v>
+      </c>
+      <c r="C35" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>92</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6">
+        <v>5100</v>
+      </c>
+      <c r="C36" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>441</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C37" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>442</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C38" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>93</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="6">
+        <v>5098</v>
+      </c>
+      <c r="C39" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>443</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>5213</v>
+      </c>
+      <c r="C40" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>444</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B41" s="6">
+        <v>5213</v>
+      </c>
+      <c r="C41" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B42" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C42" s="7">
+        <v>24932</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="6">
+        <v>4262</v>
+      </c>
+      <c r="C43" s="7">
+        <v>4262</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>95</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="6">
+        <v>2243</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3492</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="6">
+        <v>2243</v>
+      </c>
+      <c r="C45" s="7">
+        <v>3492</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>447</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="6">
+        <v>2243</v>
+      </c>
+      <c r="C46" s="7">
+        <v>3492</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>448</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="6">
+        <v>2344</v>
+      </c>
+      <c r="C47" s="7">
+        <v>3665</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>449</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="6">
+        <v>2344</v>
+      </c>
+      <c r="C48" s="7">
+        <v>3665</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="6">
+        <v>2243</v>
+      </c>
+      <c r="C49" s="7">
+        <v>3492</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>450</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="B50" s="6">
+        <v>2344</v>
+      </c>
+      <c r="C50" s="7">
+        <v>3678</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="6">
+        <v>2266</v>
+      </c>
+      <c r="C51" s="7">
+        <v>7549</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="6">
+        <v>2263</v>
+      </c>
+      <c r="C52" s="7">
+        <v>7546</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>62</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="6">
+        <v>2267</v>
+      </c>
+      <c r="C53" s="7">
+        <v>7544</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="6">
+        <v>2268</v>
+      </c>
+      <c r="C54" s="7">
+        <v>7551</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>64</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="6">
+        <v>2262</v>
+      </c>
+      <c r="C55" s="7">
+        <v>7539</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>451</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="6">
+        <v>4160</v>
+      </c>
+      <c r="C56" s="7">
+        <v>20078</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>66</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="6">
+        <v>3885</v>
+      </c>
+      <c r="C57" s="7">
+        <v>12943</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>452</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="6">
+        <v>4155</v>
+      </c>
+      <c r="C58" s="7">
+        <v>19831</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>68</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="6">
+        <v>4116</v>
+      </c>
+      <c r="C59" s="7">
+        <v>13843</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>453</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="6">
+        <v>4253</v>
+      </c>
+      <c r="C60" s="7">
+        <v>20504</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>454</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="6">
+        <v>4253</v>
+      </c>
+      <c r="C61" s="7">
+        <v>20490</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>455</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="6">
+        <v>3940</v>
+      </c>
+      <c r="C62" s="7">
+        <v>13058</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>456</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="6">
+        <v>4185</v>
+      </c>
+      <c r="C63" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>457</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B64" s="6">
+        <v>4180</v>
+      </c>
+      <c r="C64" s="7">
+        <v>19846</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="6">
+        <v>4158</v>
+      </c>
+      <c r="C65" s="7">
+        <v>20078</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>459</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="6">
+        <v>3883</v>
+      </c>
+      <c r="C66" s="7">
+        <v>12943</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>460</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="6">
+        <v>4153</v>
+      </c>
+      <c r="C67" s="7">
+        <v>20139</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>461</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="6">
+        <v>4249</v>
+      </c>
+      <c r="C68" s="7">
+        <v>20504</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>462</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="6">
+        <v>4112</v>
+      </c>
+      <c r="C69" s="7">
+        <v>13834</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>463</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="6">
+        <v>4249</v>
+      </c>
+      <c r="C70" s="7">
+        <v>20507</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>464</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="6">
+        <v>4183</v>
+      </c>
+      <c r="C71" s="7">
+        <v>20107</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>465</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="6">
+        <v>3938</v>
+      </c>
+      <c r="C72" s="7">
+        <v>13058</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>466</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="B73" s="6">
+        <v>4178</v>
+      </c>
+      <c r="C73" s="7">
+        <v>20160</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C74" s="7">
+        <v>57991</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C75" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C76" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C77" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C78" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C79" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="B80" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C80" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="6">
+        <v>2505</v>
+      </c>
+      <c r="C81" s="7">
+        <v>418</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>133</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>87</v>
+      <c r="B82" s="6">
+        <v>5218</v>
+      </c>
+      <c r="C82" s="7">
+        <v>1331</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
